--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU8"/>
+  <dimension ref="A1:AU12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.74</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
-        <v>4.04</v>
+        <v>2.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46218.79166666666</v>
+        <v>46218.58333333334</v>
       </c>
     </row>
     <row r="3">
@@ -837,12 +837,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46218.83333333334</v>
+        <v>46218.79166666666</v>
       </c>
     </row>
     <row r="4">
@@ -996,12 +996,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.61</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3.38</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>4.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46218.83333333334</v>
+        <v>46218.79166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46218.83333333334</v>
+        <v>46218.79166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46218.85416666666</v>
+        <v>46218.83333333334</v>
       </c>
     </row>
     <row r="7">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>7.75</v>
+        <v>4.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46218.875</v>
+        <v>46218.83333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1632,157 +1632,793 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Miami FC II</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="3" t="n">
+        <v>46218.83333333334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sporting JAX</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="3" t="n">
+        <v>46218.85416666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Gotham FC</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Washington Spirit</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="3" t="n">
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="3" t="n">
         <v>46218.875</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="3" t="n">
+        <v>46218.875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="3" t="n">
+        <v>46218.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.4</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>4.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.4</v>
       </c>
-      <c r="P5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>4.86</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P8" t="n">
-        <v>4.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>4.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P8" t="n">
-        <v>4.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P6" t="n">
-        <v>4.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>4.86</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.4</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T4" t="n">
         <v>3.4</v>
       </c>
-      <c r="P4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>4.86</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P8" t="n">
-        <v>4.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>4.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>4.86</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.4</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="O6" t="n">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>4.86</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P8" t="n">
-        <v>4.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1370,55 +1370,55 @@
         <v>4.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1847,55 +1847,55 @@
         <v>1.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P6" t="n">
-        <v>4.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.13</v>
+        <v>3.22</v>
       </c>
       <c r="R6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
         <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
         <v>1.11</v>
@@ -1394,47 +1394,47 @@
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>4.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>2.13</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S7" t="n">
         <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="U7" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
@@ -1553,31 +1553,31 @@
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.4</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>2.01</v>
       </c>
       <c r="O6" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>3.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>4.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.13</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
         <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
@@ -1553,47 +1553,47 @@
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.38</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.4</v>
       </c>
-      <c r="P5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.19</v>
+        <v>4.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>2.01</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>3.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P8" t="n">
-        <v>4.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.13</v>
+        <v>3.22</v>
       </c>
       <c r="R8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
         <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
         <v>1.11</v>
@@ -1712,47 +1712,47 @@
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.38</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.01</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="P7" t="n">
-        <v>3.19</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.61</v>
+        <v>2.01</v>
       </c>
       <c r="O8" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>3.19</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>4.86</v>
+        <v>3.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>3.19</v>
+        <v>4.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.01</v>
+        <v>2.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>2.01</v>
       </c>
       <c r="O7" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>3.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1688,55 +1688,55 @@
         <v>4.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="R8" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="S8" t="n">
         <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.27</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
         <v>2.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.17</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
         <v>4.2</v>
@@ -1853,10 +1853,10 @@
         <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="U9" t="n">
         <v>2.66</v>
@@ -1865,37 +1865,37 @@
         <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
         <v>3.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC9" t="n">
         <v>3.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
         <v>1.2</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>4.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.69</v>
+        <v>2.01</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2.35</v>
+        <v>3.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.01</v>
+        <v>2.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.01</v>
+        <v>2.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.69</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.35</v>
+        <v>4.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.46</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S7" t="n">
         <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
         <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="P8" t="n">
-        <v>4.86</v>
+        <v>3.19</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1</v>
+        <v>4.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.69</v>
+        <v>2.01</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2.35</v>
+        <v>3.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>2.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>4.86</v>
+        <v>2.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>3.46</v>
       </c>
       <c r="R7" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
         <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
         <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>3.19</v>
+        <v>4.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -728,10 +728,10 @@
         <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>4.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.01</v>
+        <v>2.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>3.19</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.69</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.35</v>
+        <v>4.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.46</v>
+        <v>2.21</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>2.01</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="P8" t="n">
-        <v>4.86</v>
+        <v>3.19</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1850,37 +1850,37 @@
         <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="U9" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
         <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
         <v>3.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>3.08</v>
@@ -1889,10 +1889,10 @@
         <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
         <v>2.05</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
         <v>1.2</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -728,10 +728,10 @@
         <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -887,16 +887,16 @@
         <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
         <v>1.37</v>
@@ -905,10 +905,10 @@
         <v>2.74</v>
       </c>
       <c r="U3" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
         <v>1.07</v>
@@ -917,7 +917,7 @@
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z3" t="n">
         <v>3.68</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="T4" t="n">
-        <v>3.18</v>
+        <v>2.28</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>3.55</v>
       </c>
       <c r="V4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.46</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.95</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="P7" t="n">
-        <v>4.86</v>
+        <v>3.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2.01</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="O12" t="n">
         <v>3.95</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -728,10 +728,10 @@
         <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7</v>
+        <v>4.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="U3" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
         <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.89</v>
       </c>
-      <c r="AC3" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="T4" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="U4" t="n">
-        <v>3.55</v>
+        <v>2.66</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.38</v>
+        <v>3.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.9</v>
+        <v>3.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>3.11</v>
       </c>
       <c r="R5" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="T5" t="n">
-        <v>3.18</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>4.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.69</v>
+        <v>2.01</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>3.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.01</v>
+        <v>2.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>3.19</v>
+        <v>2.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
         <v>2.21</v>
       </c>
       <c r="R8" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
         <v>1.33</v>
@@ -1700,10 +1700,10 @@
         <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
@@ -1712,31 +1712,31 @@
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB8" t="n">
         <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
         <v>2.01</v>
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>4.53</v>
       </c>
       <c r="R9" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="S9" t="n">
         <v>1.33</v>
@@ -1859,7 +1859,7 @@
         <v>2.9</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="V9" t="n">
         <v>1.4</v>
@@ -1871,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
         <v>3.45</v>
@@ -1880,7 +1880,7 @@
         <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>3.08</v>
@@ -1889,10 +1889,10 @@
         <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
         <v>2.05</v>
@@ -1911,7 +1911,7 @@
         <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="O12" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>6.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -731,7 +731,7 @@
         <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="T3" t="n">
-        <v>3.18</v>
+        <v>2.31</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44</v>
+        <v>3.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59</v>
+        <v>6.07</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>2.86</v>
+        <v>4.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.1</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AC4" t="n">
-        <v>3.36</v>
+        <v>2.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE4" t="n">
         <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
         <v>1.53</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.01</v>
+        <v>2.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>3.19</v>
+        <v>2.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.69</v>
+        <v>2.01</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="P7" t="n">
-        <v>2.31</v>
+        <v>3.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="P12" t="n">
-        <v>6.12</v>
+        <v>5.86</v>
       </c>
       <c r="Q12" t="n">
         <v>2.08</v>
@@ -2330,13 +2330,13 @@
         <v>2.15</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
         <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>2.97</v>
+        <v>2.82</v>
       </c>
       <c r="V12" t="n">
         <v>1.35</v>
@@ -2345,25 +2345,25 @@
         <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.44</v>
+        <v>3.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
         <v>1.06</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>4.04</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>4.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.1</v>
       </c>
-      <c r="S5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.69</v>
+        <v>1.57</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>2.31</v>
+        <v>4.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.46</v>
+        <v>2.21</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
         <v>1.33</v>
@@ -1382,43 +1382,43 @@
         <v>2.91</v>
       </c>
       <c r="U6" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.76</v>
+        <v>3.42</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.79</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.36</v>
+        <v>2.01</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>2.69</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>4.86</v>
+        <v>2.31</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.21</v>
+        <v>3.46</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
         <v>1.33</v>
@@ -1700,43 +1700,43 @@
         <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.01</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -731,7 +731,7 @@
         <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.88</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.31</v>
-      </c>
       <c r="U3" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.07</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
         <v>1.53</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.93</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.2</v>
+        <v>6.07</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK4" t="n">
         <v>1.53</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>5.86</v>
+        <v>5.25</v>
       </c>
       <c r="Q12" t="n">
         <v>2.08</v>
@@ -2360,7 +2360,7 @@
         <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="AD12" t="n">
         <v>1.24</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
         <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="T3" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.93</v>
+        <v>1.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>6.07</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK3" t="n">
         <v>1.53</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>3.74</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>4.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.95</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>4.04</v>
+        <v>2.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="P6" t="n">
-        <v>4.86</v>
+        <v>3.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK7" t="n">
         <v>2.01</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="R12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S12" t="n">
         <v>1.38</v>
@@ -2336,10 +2336,10 @@
         <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
         <v>1.06</v>
@@ -2348,16 +2348,16 @@
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AA12" t="n">
         <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
         <v>3.94</v>
@@ -2366,7 +2366,7 @@
         <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF12" t="n">
         <v>2.01</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -728,10 +728,10 @@
         <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="Q2" t="n">
         <v>2.95</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>3.74</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>4.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.88</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.95</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>4.04</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>3.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.06</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.93</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>6.07</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="P6" t="n">
-        <v>3.77</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="P7" t="n">
-        <v>4.86</v>
+        <v>3.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
         <v>2.31</v>
@@ -1691,7 +1691,7 @@
         <v>3.46</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
         <v>1.33</v>
@@ -1700,13 +1700,13 @@
         <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1718,7 +1718,7 @@
         <v>3.76</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
         <v>1.92</v>
@@ -1730,13 +1730,13 @@
         <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
         <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1838,49 +1838,49 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>3.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
         <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.53</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V9" t="n">
         <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
         <v>3.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>3.08</v>
@@ -1895,7 +1895,7 @@
         <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
         <v>2.11</v>
@@ -2369,10 +2369,10 @@
         <v>1.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AU16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,61 +728,61 @@
         <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.95</v>
+        <v>3.26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T2" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.36</v>
+        <v>3.02</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AB2" t="n">
         <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.32</v>
+        <v>3.72</v>
       </c>
       <c r="AD2" t="n">
         <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -837,27 +837,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>ML Vitebsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.74</v>
+        <v>5.5</v>
       </c>
       <c r="P3" t="n">
-        <v>4.04</v>
+        <v>9.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="R3" t="n">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="S3" t="n">
         <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
         <v>1.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.95</v>
+        <v>3.32</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46218.79166666666</v>
+        <v>46218.60416666666</v>
       </c>
     </row>
     <row r="4">
@@ -996,27 +996,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R4" t="n">
         <v>2.3</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.1</v>
-      </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46218.79166666666</v>
+        <v>46218.63541666666</v>
       </c>
     </row>
     <row r="5">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>4.43</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>3.22</v>
       </c>
       <c r="U5" t="n">
-        <v>3.42</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.6</v>
+        <v>4.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.45</v>
+        <v>1.69</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>2.13</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.07</v>
+        <v>2.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46218.79166666666</v>
+        <v>46218.66666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1314,27 +1314,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Petrocub</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.3</v>
       </c>
-      <c r="T6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.44</v>
-      </c>
       <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.07</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.73</v>
+        <v>2.72</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.63</v>
+        <v>4.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.64</v>
+        <v>2.06</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46218.83333333334</v>
+        <v>46218.66666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.64</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>3.77</v>
+        <v>2.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46218.83333333334</v>
+        <v>46218.79166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.46</v>
+        <v>2.88</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>2.4</v>
       </c>
       <c r="U8" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.76</v>
+        <v>2.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.92</v>
+        <v>6.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.11</v>
+        <v>1.63</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46218.83333333334</v>
+        <v>46218.79166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.89</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>4.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T9" t="n">
-        <v>3.01</v>
+        <v>3.18</v>
       </c>
       <c r="U9" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.2</v>
+        <v>1.95</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46218.85416666666</v>
+        <v>46218.79166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>7.75</v>
+        <v>3.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46218.875</v>
+        <v>46218.83333333334</v>
       </c>
     </row>
     <row r="11">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46218.875</v>
+        <v>46218.83333333334</v>
       </c>
     </row>
     <row r="12">
@@ -2268,156 +2268,792 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="3" t="n">
+        <v>46218.83333333334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sporting JAX</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="3" t="n">
+        <v>46218.85416666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="3" t="n">
+        <v>46218.875</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Gotham FC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Washington Spirit</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="3" t="n">
+        <v>46218.875</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Guayaquil City FC</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="N16" t="n">
         <v>1.53</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O16" t="n">
         <v>3.7</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P16" t="n">
         <v>5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="Q16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R16" t="n">
         <v>2.14</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S16" t="n">
         <v>1.38</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="T16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U16" t="n">
         <v>2.88</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W12" t="n">
+      <c r="V16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.06</v>
       </c>
-      <c r="X12" t="n">
+      <c r="X16" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y16" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="Z16" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.02</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AB16" t="n">
         <v>1.77</v>
       </c>
-      <c r="AC12" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AC16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AE16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AJ16" t="n">
         <v>1.19</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AK16" t="n">
         <v>2.24</v>
       </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" s="3" t="n">
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="3" t="n">
         <v>46218.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>3.81</v>
+        <v>4.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>1.78</v>
       </c>
       <c r="O11" t="n">
-        <v>3.23</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>3.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.63</v>
+        <v>2.72</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="P12" t="n">
-        <v>4.56</v>
+        <v>2.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.17</v>
+        <v>3.46</v>
       </c>
       <c r="R12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S12" t="n">
         <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V12" t="n">
         <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.26</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="S2" t="n">
         <v>1.44</v>
@@ -746,44 +746,44 @@
         <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.04</v>
       </c>
-      <c r="X2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AF2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
         <v>5.5</v>
       </c>
       <c r="P3" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q3" t="n">
         <v>1.67</v>
@@ -899,49 +899,49 @@
         <v>2.63</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
         <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
         <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
         <v>2.44</v>
@@ -1082,10 +1082,10 @@
         <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
         <v>2.74</v>
@@ -1100,7 +1100,7 @@
         <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Petrocub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q5" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.3</v>
       </c>
-      <c r="T5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.17</v>
+        <v>2.02</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Petrocub</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>4.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.28</v>
-      </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>3.22</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.72</v>
+        <v>4.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.16</v>
+        <v>1.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.15</v>
+        <v>2.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.33</v>
+        <v>4.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.88</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="S8" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.48</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.46</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.19</v>
       </c>
       <c r="P9" t="n">
-        <v>4.04</v>
+        <v>2.74</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.98</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2795,61 +2795,61 @@
         <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="S15" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.42</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q16" t="n">
         <v>2.1</v>
       </c>
       <c r="R16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T16" t="n">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
         <v>2.88</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.19</v>
+        <v>2.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Petrocub</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>4.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.28</v>
+        <v>4.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3.22</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.72</v>
+        <v>4.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>2.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.02</v>
+        <v>1.17</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Petrocub</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.45</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.6</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.34</v>
+        <v>3.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.33</v>
+        <v>2.72</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.57</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>2.06</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.13</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.17</v>
+        <v>2.02</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.19</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.46</v>
+        <v>3.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>3.19</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>2.74</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.71</v>
+        <v>2.46</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="P10" t="n">
-        <v>4.56</v>
+        <v>3.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="U10" t="n">
         <v>2.5</v>
@@ -2027,34 +2027,34 @@
         <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2315,34 +2315,34 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="O12" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
         <v>3.46</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="S12" t="n">
         <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>2.91</v>
+        <v>3.16</v>
       </c>
       <c r="U12" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -2351,19 +2351,19 @@
         <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="AA12" t="n">
         <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE12" t="n">
         <v>1.12</v>
@@ -2372,7 +2372,7 @@
         <v>1.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.32</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.2</v>
+        <v>4.73</v>
       </c>
       <c r="R13" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="S13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T13" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="U13" t="n">
         <v>2.75</v>
@@ -2501,10 +2501,10 @@
         <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
         <v>1.22</v>
@@ -2513,25 +2513,25 @@
         <v>3.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD13" t="n">
         <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="R15" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>3.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.87</v>
+        <v>3.78</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.83</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="P3" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
         <v>1.67</v>
@@ -914,34 +914,34 @@
         <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AC3" t="n">
         <v>2.34</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,52 +1043,52 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
         <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V4" t="n">
         <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
         <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB4" t="n">
         <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="AD4" t="n">
         <v>1.42</v>
@@ -1097,7 +1097,7 @@
         <v>1.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
         <v>2.25</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.6</v>
+        <v>4.26</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S5" t="n">
         <v>1.31</v>
@@ -1223,7 +1223,7 @@
         <v>3.15</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V5" t="n">
         <v>1.53</v>
@@ -1238,28 +1238,28 @@
         <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
         <v>1.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
         <v>1.17</v>
@@ -1367,7 +1367,7 @@
         <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="Q6" t="n">
         <v>2.28</v>
@@ -1388,7 +1388,7 @@
         <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
         <v>1.07</v>
@@ -1397,10 +1397,10 @@
         <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
         <v>1.65</v>
@@ -1412,10 +1412,10 @@
         <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AG6" t="n">
         <v>1.7</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.19</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.74</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.71</v>
+        <v>2.46</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.19</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.46</v>
+        <v>3.71</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="O10" t="n">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="R14" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>3.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.87</v>
+        <v>3.78</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.83</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="S15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.36</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="AB15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.33</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>3.45</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O2" t="n">
         <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S2" t="n">
         <v>1.44</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U2" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="AB2" t="n">
         <v>1.66</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="P7" t="n">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.88</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.46</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.61</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.98</v>
+        <v>3.12</v>
       </c>
       <c r="R8" t="n">
-        <v>2.26</v>
+        <v>1.82</v>
       </c>
       <c r="S8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.29</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="O9" t="n">
-        <v>3.19</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>2.74</v>
+        <v>4.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.71</v>
+        <v>2.46</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,46 +2156,46 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.61</v>
+        <v>2.71</v>
       </c>
       <c r="O11" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>3.46</v>
       </c>
       <c r="R11" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
         <v>2</v>
@@ -2204,32 +2204,32 @@
         <v>2.88</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.04</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.71</v>
+        <v>1.77</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2792,34 +2792,34 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>9.15</v>
       </c>
       <c r="Q15" t="n">
         <v>1.57</v>
       </c>
       <c r="R15" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="S15" t="n">
         <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2828,7 +2828,7 @@
         <v>1.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA15" t="n">
         <v>1.36</v>
@@ -2840,16 +2840,16 @@
         <v>1.87</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.83</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,37 +2951,37 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="O16" t="n">
-        <v>3.53</v>
+        <v>3.84</v>
       </c>
       <c r="P16" t="n">
-        <v>4.9</v>
+        <v>5.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="R16" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="S16" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
         <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
         <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
         <v>1.25</v>
@@ -2990,25 +2990,25 @@
         <v>2.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
         <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Petrocub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q5" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="AC5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.17</v>
+        <v>2.06</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Petrocub</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P6" t="n">
-        <v>4.9</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>4.26</v>
       </c>
       <c r="R6" t="n">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="S6" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>3.22</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.41</v>
       </c>
-      <c r="Z6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.06</v>
+        <v>1.17</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="O7" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.68</v>
+        <v>4.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.91</v>
+        <v>2.46</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
         <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.43</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.46</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>3.12</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>1.97</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>3.58</v>
       </c>
       <c r="V9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.53</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -725,52 +725,52 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="P2" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="S2" t="n">
         <v>1.44</v>
       </c>
       <c r="T2" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="U2" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.06</v>
+        <v>2.38</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AB2" t="n">
         <v>1.66</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="AD2" t="n">
         <v>1.21</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>5.45</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R3" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="S3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="U3" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="V3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
         <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
         <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.76</v>
+        <v>2.53</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Petrocub</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.28</v>
+        <v>4.11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="S5" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.6</v>
       </c>
-      <c r="U5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.06</v>
+        <v>1.14</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Petrocub</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q6" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="AC6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.17</v>
+        <v>2.06</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,37 +1520,37 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O7" t="n">
         <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="R7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.3</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.38</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
         <v>1.18</v>
@@ -1568,16 +1568,16 @@
         <v>2.46</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
         <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="P8" t="n">
-        <v>2.68</v>
+        <v>3.19</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S8" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>2.51</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.74</v>
+        <v>2.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="O9" t="n">
         <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="T9" t="n">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.64</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>3.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T10" t="n">
-        <v>3.21</v>
+        <v>2.91</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB10" t="n">
         <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.04</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.71</v>
+        <v>1.61</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.46</v>
+        <v>2.15</v>
       </c>
       <c r="R11" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.16</v>
+        <v>3.08</v>
       </c>
       <c r="U11" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
         <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="O12" t="n">
         <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2474,58 +2474,58 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>4.07</v>
       </c>
       <c r="O13" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="P13" t="n">
         <v>1.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.73</v>
+        <v>4.8</v>
       </c>
       <c r="R13" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S13" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="T13" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="U13" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
         <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
         <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
         <v>1.73</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3</v>
+        <v>9.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.63</v>
+        <v>1.69</v>
       </c>
       <c r="R14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U14" t="n">
         <v>2</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.36</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="AB14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.33</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
         <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.2</v>
+        <v>2.08</v>
       </c>
       <c r="O15" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>9.15</v>
+        <v>3.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="R15" t="n">
-        <v>2.56</v>
+        <v>2.03</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="T15" t="n">
-        <v>4.4</v>
+        <v>2.68</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="V15" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.22</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,46 +2951,46 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="O16" t="n">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>5.81</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
         <v>2.11</v>
       </c>
       <c r="R16" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>1.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB16" t="n">
         <v>1.75</v>
@@ -3005,10 +3005,10 @@
         <v>1.06</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O3" t="n">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="P3" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
         <v>1.62</v>
@@ -899,19 +899,19 @@
         <v>2.54</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T3" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
@@ -929,16 +929,16 @@
         <v>2.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AD3" t="n">
         <v>1.48</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>1.68</v>
@@ -957,7 +957,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
         <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Petrocub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>1.73</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.11</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>2.14</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Petrocub</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.7</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AA6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB6" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>2.59</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.06</v>
+        <v>1.17</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>2.93</v>
       </c>
       <c r="P7" t="n">
-        <v>4.2</v>
+        <v>3.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>3.12</v>
+        <v>2.45</v>
       </c>
       <c r="U7" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="V7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.5</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC7" t="n">
-        <v>2.46</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>2.09</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.15</v>
       </c>
-      <c r="O8" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="S8" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
-        <v>3.58</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.51</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.09</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1997,58 +1997,58 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="R10" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
         <v>1.58</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P11" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
         <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="V11" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK11" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.05</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.07</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T13" t="n">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="U13" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V13" t="n">
         <v>1.43</v>
@@ -2507,31 +2507,31 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z13" t="n">
         <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.87</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Petrocub</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.73</v>
+        <v>4.05</v>
       </c>
       <c r="O5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.3</v>
       </c>
-      <c r="P5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.45</v>
-      </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.01</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.26</v>
+        <v>1.64</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>2.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.04</v>
+        <v>1.17</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Petrocub</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.05</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.22</v>
+        <v>2.36</v>
       </c>
       <c r="R6" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.17</v>
+        <v>2.04</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="P7" t="n">
-        <v>3.19</v>
+        <v>2.74</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.8</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.45</v>
-      </c>
       <c r="U7" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.51</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.09</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF7" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.57</v>
+        <v>2.15</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="P9" t="n">
-        <v>2.74</v>
+        <v>3.19</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="S9" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>2.51</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.69</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.66</v>
+        <v>2.69</v>
       </c>
       <c r="O11" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>3.48</v>
       </c>
       <c r="R11" t="n">
         <v>2.25</v>
       </c>
       <c r="S11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.3</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.23</v>
-      </c>
       <c r="Z11" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA11" t="n">
         <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P12" t="n">
-        <v>4.32</v>
+        <v>4.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Petrocub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.05</v>
+        <v>1.73</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.22</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.17</v>
+        <v>2.04</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Petrocub</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>4.05</v>
       </c>
       <c r="O6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.3</v>
       </c>
-      <c r="P6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.45</v>
-      </c>
       <c r="U6" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="W6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.01</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.26</v>
+        <v>1.64</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>2.59</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.04</v>
+        <v>1.17</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.57</v>
+        <v>2.15</v>
       </c>
       <c r="O7" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="P7" t="n">
-        <v>2.74</v>
+        <v>3.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="U7" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>2.51</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>2.72</v>
       </c>
       <c r="R8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="T8" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.15</v>
       </c>
-      <c r="O9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="S9" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="T9" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="U9" t="n">
-        <v>3.58</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.51</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.09</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>2.69</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.32</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.69</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.22</v>
       </c>
-      <c r="O14" t="n">
-        <v>6</v>
-      </c>
-      <c r="P14" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.08</v>
+        <v>1.22</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>3.21</v>
+        <v>9.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.63</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="S15" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.68</v>
+        <v>4.3</v>
       </c>
       <c r="U15" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.33</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.73</v>
+        <v>3.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T2" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="U2" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
         <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,61 +884,61 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="Q3" t="n">
         <v>1.62</v>
       </c>
       <c r="R3" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="S3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
         <v>1.68</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,34 +1043,34 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.3</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.39</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
@@ -1082,22 +1082,22 @@
         <v>4.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
         <v>2.23</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,61 +1202,61 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T5" t="n">
         <v>2.45</v>
       </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
         <v>2.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
         <v>1.67</v>
@@ -1275,7 +1275,7 @@
         <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.22</v>
+        <v>5.34</v>
       </c>
       <c r="R6" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
         <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.12</v>
@@ -1397,44 +1397,44 @@
         <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB6" t="n">
         <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.17</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.15</v>
+        <v>2.71</v>
       </c>
       <c r="O7" t="n">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>3.19</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>3.58</v>
+        <v>2.95</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.57</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.72</v>
+        <v>3.18</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
         <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>2.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.05</v>
+        <v>5.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.37</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.15</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.15</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.69</v>
+        <v>1.58</v>
       </c>
       <c r="O10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.2</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
       <c r="U10" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>1.96</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>2.77</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>4.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="O12" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2486,19 +2486,19 @@
         <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U13" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="V13" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
@@ -2510,28 +2510,28 @@
         <v>1.23</v>
       </c>
       <c r="Z13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC13" t="n">
         <v>3.6</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AG13" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="P14" t="n">
-        <v>3.21</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="R14" t="n">
-        <v>2.03</v>
+        <v>2.73</v>
       </c>
       <c r="S14" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="T14" t="n">
-        <v>2.68</v>
+        <v>4.6</v>
       </c>
       <c r="U14" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>6.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.84</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.22</v>
+        <v>2.35</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3.12</v>
       </c>
       <c r="P15" t="n">
-        <v>9.5</v>
+        <v>3.61</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="S15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.18</v>
       </c>
-      <c r="T15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AE15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.33</v>
       </c>
-      <c r="AF15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK15" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="O16" t="n">
         <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>6.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S16" t="n">
         <v>1.4</v>
@@ -2972,43 +2972,43 @@
         <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC16" t="n">
         <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -714,14 +714,14 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46218.58333333334</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -873,14 +873,14 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46218.60416666666</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Petrocub</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>4.8</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.4</v>
       </c>
-      <c r="R5" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AC5" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>1.14</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Petrocub</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.61</v>
+        <v>4.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.34</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="T6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
-        <v>2.4</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>2.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.14</v>
+        <v>2.05</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R7" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>2.95</v>
+        <v>3.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.21</v>
+        <v>4.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.75</v>
       </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.38</v>
-      </c>
       <c r="U8" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
         <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.77</v>
+        <v>1.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.19</v>
+        <v>3.54</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.17</v>
+        <v>2.35</v>
       </c>
       <c r="O14" t="n">
-        <v>5.75</v>
+        <v>3.12</v>
       </c>
       <c r="P14" t="n">
-        <v>8.050000000000001</v>
+        <v>3.61</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.73</v>
+        <v>2.04</v>
       </c>
       <c r="S14" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.82</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.06</v>
       </c>
-      <c r="Z14" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.35</v>
+        <v>1.17</v>
       </c>
       <c r="O15" t="n">
-        <v>3.12</v>
+        <v>5.75</v>
       </c>
       <c r="P15" t="n">
-        <v>3.61</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="R15" t="n">
-        <v>2.04</v>
+        <v>2.73</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="T15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2.75</v>
       </c>
-      <c r="U15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>1.94</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.84</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-15.xlsx
+++ b/jogos_2026-07-15.xlsx
@@ -1020,26 +1020,26 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '59']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46218.63541666666</v>
@@ -1170,139 +1170,139 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Petrocub</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>1.67</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>4.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.34</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="T5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U5" t="n">
         <v>3</v>
       </c>
-      <c r="U5" t="n">
-        <v>2.4</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '31', '44', '59', '84', '90']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>2.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.14</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46218.66666666666</v>
@@ -1329,19 +1329,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Petrocub</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1353,115 +1353,115 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>4.8</v>
+        <v>1.61</v>
       </c>
       <c r="Q6" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.4</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB6" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AC6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>['68', '82']</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
         <v>4</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AO6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AR6" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46218.66666666666</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>4.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
-        <v>1.73</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK7" t="n">
         <v>2.3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.55</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>4.55</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>3.72</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>1.51</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.65</v>
+        <v>2.26</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.63</v>
+        <v>4.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.58</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.77</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
         <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.35</v>
+        <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>3.12</v>
+        <v>5.75</v>
       </c>
       <c r="P14" t="n">
-        <v>3.61</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="R14" t="n">
-        <v>2.04</v>
+        <v>2.73</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="T14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB14" t="n">
         <v>2.75</v>
       </c>
-      <c r="U14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3</v>
+        <v>1.94</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.84</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.17</v>
+        <v>2.35</v>
       </c>
       <c r="O15" t="n">
-        <v>5.75</v>
+        <v>3.12</v>
       </c>
       <c r="P15" t="n">
-        <v>8.050000000000001</v>
+        <v>3.61</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.73</v>
+        <v>2.04</v>
       </c>
       <c r="S15" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.82</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.06</v>
       </c>
-      <c r="Z15" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>6.17</v>
+        <v>5.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
         <v>2.15</v>
@@ -2972,10 +2972,10 @@
         <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
         <v>1.07</v>
@@ -2990,25 +2990,25 @@
         <v>3.04</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
         <v>1.74</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
         <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
